--- a/data/petscii/symbols.xlsx
+++ b/data/petscii/symbols.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lollo\Svil\GitHub\tomba-azteca\data\petscii\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A95FC36-F04B-46A9-BA5C-D355A7A05203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7424EBCF-8926-4CA2-A308-F5B68E7CA180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33708" yWindow="3936" windowWidth="23040" windowHeight="12120" xr2:uid="{D4152578-70BF-4B16-B858-04D7E334D362}"/>
+    <workbookView xWindow="6432" yWindow="4152" windowWidth="23040" windowHeight="12120" xr2:uid="{D4152578-70BF-4B16-B858-04D7E334D362}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
   <si>
     <t>@</t>
   </si>
@@ -244,13 +244,49 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>−</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +304,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -290,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -302,6 +345,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1520,6 +1566,56 @@
         <v>80</v>
       </c>
     </row>
+    <row r="17" spans="8:44" x14ac:dyDescent="0.3">
+      <c r="H17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="19" spans="8:44" x14ac:dyDescent="0.3">
       <c r="H19" s="1">
         <f>W16+1</f>
@@ -1648,6 +1744,44 @@
       <c r="AR19" s="1">
         <f t="shared" si="11"/>
         <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="8:44" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="8:44" x14ac:dyDescent="0.3">
